--- a/Fiche de mouvement _05-2026.xlsx
+++ b/Fiche de mouvement _05-2026.xlsx
@@ -1,31 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ab0b5a2ed962cae/Documents/Samir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9093D7-F298-42E1-9CBE-BCD68AB63A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{7D9093D7-F298-42E1-9CBE-BCD68AB63A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C293366A-770B-4B46-9569-22445E398944}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20-05" sheetId="10" r:id="rId1"/>
-    <sheet name="21-05" sheetId="2" r:id="rId2"/>
-    <sheet name="24-05" sheetId="3" r:id="rId3"/>
-    <sheet name="25-05" sheetId="4" r:id="rId4"/>
-    <sheet name="26-05" sheetId="5" r:id="rId5"/>
-    <sheet name="31-05" sheetId="6" r:id="rId6"/>
+    <sheet name="DASHBOARD" sheetId="11" r:id="rId1"/>
+    <sheet name="20-05" sheetId="10" r:id="rId2"/>
+    <sheet name="21-05" sheetId="2" r:id="rId3"/>
+    <sheet name="24-05" sheetId="3" r:id="rId4"/>
+    <sheet name="25-05" sheetId="4" r:id="rId5"/>
+    <sheet name="26-05" sheetId="5" r:id="rId6"/>
+    <sheet name="31-05" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="167">
   <si>
     <t>N° Conteneur</t>
   </si>
@@ -502,16 +516,42 @@
   </si>
   <si>
     <t>GROUPAGE</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>TC Réceptionnés</t>
+  </si>
+  <si>
+    <t>TC Sortis</t>
+  </si>
+  <si>
+    <t>Total Mouvements</t>
+  </si>
+  <si>
+    <t>TC Sortis
+VIDE</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>VH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="##&quot;/&quot;##&quot;/&quot;####"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -570,8 +610,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2C3E50"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,8 +645,44 @@
         <bgColor rgb="FF2C3E50"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B365D"/>
+        <bgColor rgb="FF1B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9F9"/>
+        <bgColor rgb="FFF8F9F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+        <bgColor rgb="FFD6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF3CF"/>
+        <bgColor rgb="FFFCF3CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED0000"/>
+        <bgColor rgb="FF2C3E50"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -809,13 +906,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDC3C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDC3C7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBDC3C7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBDC3C7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -946,18 +1058,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -2427,9 +2557,311 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{952FD1DC-DCCD-48EE-93A2-9334C15076EB}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47" style="45" customWidth="1"/>
+    <col min="2" max="2" width="18" style="45" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" style="45" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="45" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="46">
+        <v>46162</v>
+      </c>
+      <c r="B2" s="47">
+        <f>'20-05'!H1</f>
+        <v>33</v>
+      </c>
+      <c r="C2" s="47">
+        <f>'20-05'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="48">
+        <f t="shared" ref="D2:D7" si="0">SUM(B2:C2)</f>
+        <v>33</v>
+      </c>
+      <c r="F2" s="47"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="46">
+        <v>46163</v>
+      </c>
+      <c r="B3" s="47">
+        <f>'21-05'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C3" s="47">
+        <f>'21-05'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D3" s="48">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F3" s="47"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="46">
+        <v>46166</v>
+      </c>
+      <c r="B4" s="47">
+        <f>'24-05'!H1</f>
+        <v>9</v>
+      </c>
+      <c r="C4" s="47">
+        <f>'24-05'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="48">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="F4" s="47"/>
+    </row>
+    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="46">
+        <v>46167</v>
+      </c>
+      <c r="B5" s="47">
+        <f>'25-05'!H1</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="47">
+        <f>'25-05'!H2</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="48">
+        <f t="shared" ref="D5" si="1">SUM(B5:C5)</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="47"/>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="46">
+        <v>46168</v>
+      </c>
+      <c r="B6" s="47">
+        <f>'26-05'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C6" s="47">
+        <f>'26-05'!H2</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="48">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="47"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="46">
+        <v>46173</v>
+      </c>
+      <c r="B7" s="47">
+        <f>'31-05'!H1</f>
+        <v>3</v>
+      </c>
+      <c r="C7" s="47">
+        <f>'31-05'!H2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="48">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="47"/>
+    </row>
+    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="46">
+        <v>46167</v>
+      </c>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+      <c r="F8" s="47"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="46">
+        <v>46274</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+      <c r="F9" s="47"/>
+    </row>
+    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="46">
+        <v>46275</v>
+      </c>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+      <c r="F10" s="47"/>
+    </row>
+    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="46">
+        <v>46274</v>
+      </c>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
+      <c r="F11" s="47"/>
+    </row>
+    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="46">
+        <v>46275</v>
+      </c>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48"/>
+      <c r="F12" s="47"/>
+    </row>
+    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="46">
+        <v>46276</v>
+      </c>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="F13" s="47"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="46">
+        <v>46277</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48"/>
+      <c r="F14" s="47"/>
+    </row>
+    <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="46">
+        <v>46278</v>
+      </c>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="48"/>
+      <c r="F15" s="47"/>
+    </row>
+    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="46">
+        <v>46279</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="48"/>
+      <c r="F16" s="47"/>
+    </row>
+    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="46">
+        <v>46280</v>
+      </c>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="48"/>
+      <c r="F17" s="47"/>
+    </row>
+    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="46">
+        <v>46281</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="48"/>
+      <c r="F18" s="47"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="46">
+        <v>46282</v>
+      </c>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="F19" s="47"/>
+    </row>
+    <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="46">
+        <v>46283</v>
+      </c>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="F20" s="47"/>
+    </row>
+    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="46">
+        <v>46284</v>
+      </c>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="48"/>
+      <c r="F21" s="47"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="46">
+        <v>46285</v>
+      </c>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="48"/>
+      <c r="F22" s="47"/>
+    </row>
+    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="F23" s="47"/>
+    </row>
+    <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="49">
+        <f>SUM(B2:B22)</f>
+        <v>51</v>
+      </c>
+      <c r="C24" s="49">
+        <f>SUM(C2:C22)</f>
+        <v>5</v>
+      </c>
+      <c r="D24" s="49">
+        <f>SUM(D2:D22)</f>
+        <v>56</v>
+      </c>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6F2A67B-F865-4732-AD11-694DBC696C2F}">
-  <dimension ref="A1:H84"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J84"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -2440,13 +2872,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(B9:B41,"&lt;&gt;")</f>
+        <v>33</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -2458,13 +2915,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -2473,11 +2930,11 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -2497,7 +2954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39">
         <v>1</v>
       </c>
@@ -2515,7 +2972,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2</v>
       </c>
@@ -2533,7 +2990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>3</v>
       </c>
@@ -2551,7 +3008,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>4</v>
       </c>
@@ -2569,7 +3026,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>5</v>
       </c>
@@ -2587,7 +3044,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>6</v>
       </c>
@@ -2605,7 +3062,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>7</v>
       </c>
@@ -2623,7 +3080,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>8</v>
       </c>
@@ -2641,7 +3098,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="17" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>9</v>
       </c>
@@ -2659,7 +3116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="18" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>10</v>
       </c>
@@ -2677,7 +3134,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>11</v>
       </c>
@@ -2695,7 +3152,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>12</v>
       </c>
@@ -2713,7 +3170,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>13</v>
       </c>
@@ -2731,7 +3188,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="22" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>14</v>
       </c>
@@ -2749,7 +3206,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="23" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>15</v>
       </c>
@@ -2767,7 +3224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>16</v>
       </c>
@@ -2785,7 +3242,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>17</v>
       </c>
@@ -2803,7 +3260,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="26" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>18</v>
       </c>
@@ -2821,7 +3278,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="27" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>19</v>
       </c>
@@ -2839,7 +3296,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="28" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>20</v>
       </c>
@@ -2857,7 +3314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="29" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>21</v>
       </c>
@@ -2875,7 +3332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="30" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>22</v>
       </c>
@@ -2893,7 +3350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>23</v>
       </c>
@@ -2911,7 +3368,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="32" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>24</v>
       </c>
@@ -2929,7 +3386,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="33" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>25</v>
       </c>
@@ -2947,7 +3404,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="34" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>26</v>
       </c>
@@ -2965,7 +3422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="35" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>27</v>
       </c>
@@ -2983,7 +3440,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="36" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>28</v>
       </c>
@@ -3001,7 +3458,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="37" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>29</v>
       </c>
@@ -3019,7 +3476,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="38" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>30</v>
       </c>
@@ -3037,7 +3494,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="39" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>31</v>
       </c>
@@ -3055,7 +3512,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="40" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>32</v>
       </c>
@@ -3073,7 +3530,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="41" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>33</v>
       </c>
@@ -3091,7 +3548,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="42" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="40"/>
       <c r="C42" s="40"/>
@@ -3099,7 +3556,7 @@
       <c r="E42" s="40"/>
       <c r="F42" s="41"/>
     </row>
-    <row r="43" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="43" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="40"/>
       <c r="C43" s="40"/>
@@ -3107,7 +3564,7 @@
       <c r="E43" s="40"/>
       <c r="F43" s="41"/>
     </row>
-    <row r="44" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="44" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="40"/>
       <c r="C44" s="40"/>
@@ -3115,7 +3572,7 @@
       <c r="E44" s="40"/>
       <c r="F44" s="41"/>
     </row>
-    <row r="45" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="45" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="40"/>
       <c r="C45" s="40"/>
@@ -3123,7 +3580,7 @@
       <c r="E45" s="40"/>
       <c r="F45" s="41"/>
     </row>
-    <row r="46" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="46" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="40"/>
       <c r="C46" s="40"/>
@@ -3131,7 +3588,7 @@
       <c r="E46" s="40"/>
       <c r="F46" s="41"/>
     </row>
-    <row r="47" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="47" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="40"/>
       <c r="C47" s="40"/>
@@ -3139,7 +3596,7 @@
       <c r="E47" s="40"/>
       <c r="F47" s="41"/>
     </row>
-    <row r="48" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="48" spans="1:6" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="40"/>
       <c r="C48" s="40"/>
@@ -3147,7 +3604,7 @@
       <c r="E48" s="40"/>
       <c r="F48" s="41"/>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="49" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="40"/>
       <c r="C49" s="40"/>
@@ -3155,7 +3612,7 @@
       <c r="E49" s="40"/>
       <c r="F49" s="41"/>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="50" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="40"/>
       <c r="C50" s="40"/>
@@ -3163,7 +3620,7 @@
       <c r="E50" s="40"/>
       <c r="F50" s="41"/>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="51" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="40"/>
       <c r="C51" s="40"/>
@@ -3171,7 +3628,7 @@
       <c r="E51" s="40"/>
       <c r="F51" s="41"/>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="52" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="40"/>
       <c r="C52" s="40"/>
@@ -3179,7 +3636,7 @@
       <c r="E52" s="40"/>
       <c r="F52" s="41"/>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="53" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="40"/>
       <c r="C53" s="40"/>
@@ -3187,7 +3644,7 @@
       <c r="E53" s="40"/>
       <c r="F53" s="41"/>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="54" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="40"/>
       <c r="C54" s="40"/>
@@ -3195,7 +3652,7 @@
       <c r="E54" s="40"/>
       <c r="F54" s="41"/>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="55" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="40"/>
       <c r="C55" s="40"/>
@@ -3203,7 +3660,7 @@
       <c r="E55" s="40"/>
       <c r="F55" s="41"/>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="56" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="40"/>
       <c r="C56" s="40"/>
@@ -3211,7 +3668,7 @@
       <c r="E56" s="40"/>
       <c r="F56" s="41"/>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="57" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="40"/>
       <c r="C57" s="40"/>
@@ -3219,7 +3676,7 @@
       <c r="E57" s="40"/>
       <c r="F57" s="41"/>
     </row>
-    <row r="60" spans="1:7" ht="15.75">
+    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="5"/>
       <c r="C60" s="1"/>
@@ -3228,7 +3685,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
     </row>
-    <row r="61" spans="1:7" ht="15.75">
+    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="24" t="s">
         <v>40</v>
@@ -3238,7 +3695,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
     </row>
-    <row r="62" spans="1:7" ht="15.75" thickBot="1">
+    <row r="62" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="2"/>
       <c r="C62" s="1"/>
@@ -3247,7 +3704,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1">
+    <row r="63" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>36</v>
       </c>
@@ -3267,7 +3724,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.95" customHeight="1">
+    <row r="64" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="19">
         <v>1</v>
       </c>
@@ -3287,7 +3744,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.95" customHeight="1">
+    <row r="65" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17">
         <v>2</v>
       </c>
@@ -3307,7 +3764,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.95" customHeight="1">
+    <row r="66" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="17"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -3315,7 +3772,7 @@
       <c r="E66" s="9"/>
       <c r="F66" s="18"/>
     </row>
-    <row r="67" spans="1:7" ht="15.95" customHeight="1">
+    <row r="67" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -3323,7 +3780,7 @@
       <c r="E67" s="9"/>
       <c r="F67" s="18"/>
     </row>
-    <row r="68" spans="1:7" ht="15.95" customHeight="1">
+    <row r="68" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -3331,7 +3788,7 @@
       <c r="E68" s="9"/>
       <c r="F68" s="18"/>
     </row>
-    <row r="69" spans="1:7" ht="15.95" customHeight="1" thickBot="1">
+    <row r="69" spans="1:7" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -3339,7 +3796,7 @@
       <c r="E69" s="11"/>
       <c r="F69" s="22"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3348,7 +3805,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="1:7" ht="15.75">
+    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="24" t="s">
         <v>41</v>
@@ -3358,7 +3815,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="5"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" thickBot="1">
+    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="2"/>
       <c r="C74" s="1"/>
@@ -3367,7 +3824,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="1:7" ht="15.75" thickBot="1">
+    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>36</v>
       </c>
@@ -3387,7 +3844,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.95" customHeight="1">
+    <row r="76" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="19">
         <v>1</v>
       </c>
@@ -3405,7 +3862,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.95" customHeight="1">
+    <row r="77" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17">
         <v>2</v>
       </c>
@@ -3423,7 +3880,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15.95" customHeight="1">
+    <row r="78" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="17">
         <v>3</v>
       </c>
@@ -3441,7 +3898,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15.95" customHeight="1">
+    <row r="79" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17">
         <v>4</v>
       </c>
@@ -3459,7 +3916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15.95" customHeight="1">
+    <row r="80" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="17">
         <v>5</v>
       </c>
@@ -3477,7 +3934,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="15.95" customHeight="1">
+    <row r="81" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17">
         <v>6</v>
       </c>
@@ -3495,7 +3952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="15.75" customHeight="1">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="17">
         <v>7</v>
       </c>
@@ -3513,7 +3970,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="15.95" customHeight="1">
+    <row r="83" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17"/>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
@@ -3521,7 +3978,7 @@
       <c r="E83" s="31"/>
       <c r="F83" s="33"/>
     </row>
-    <row r="84" spans="1:6" ht="15.75" thickBot="1">
+    <row r="84" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="21"/>
       <c r="B84" s="32"/>
       <c r="C84" s="32"/>
@@ -3534,7 +3991,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>LEFT(CELL("format",B9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3543,11 +4000,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B42777-B304-42F4-93E6-C7832DBF0AFF}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -3558,13 +4015,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(C9:C16,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -3576,13 +4058,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -3591,11 +4073,11 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>36</v>
       </c>
@@ -3615,7 +4097,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -3635,7 +4117,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -3655,7 +4137,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -3675,7 +4157,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -3683,7 +4165,7 @@
       <c r="E12" s="9"/>
       <c r="F12" s="28"/>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -3691,7 +4173,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="28"/>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.95" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21"/>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -3699,7 +4181,7 @@
       <c r="E14" s="11"/>
       <c r="F14" s="29"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -3708,7 +4190,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="24" t="s">
         <v>40</v>
@@ -3718,7 +4200,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -3727,7 +4209,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>36</v>
       </c>
@@ -3747,7 +4229,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.95" customHeight="1">
+    <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>1</v>
       </c>
@@ -3767,7 +4249,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.95" customHeight="1">
+    <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>2</v>
       </c>
@@ -3787,7 +4269,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.95" customHeight="1">
+    <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -3795,7 +4277,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:7" ht="15.95" customHeight="1">
+    <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -3803,7 +4285,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:7" ht="15.95" customHeight="1">
+    <row r="25" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -3811,7 +4293,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:7" ht="15.95" customHeight="1" thickBot="1">
+    <row r="26" spans="1:7" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3819,7 +4301,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3828,7 +4310,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="24" t="s">
         <v>155</v>
@@ -3838,7 +4320,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -3847,7 +4329,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -3867,7 +4349,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.95" customHeight="1">
+    <row r="33" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19">
         <v>1</v>
       </c>
@@ -3885,7 +4367,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.95" customHeight="1">
+    <row r="34" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>2</v>
       </c>
@@ -3903,7 +4385,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.95" customHeight="1">
+    <row r="35" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>3</v>
       </c>
@@ -3921,7 +4403,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.95" customHeight="1">
+    <row r="36" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>4</v>
       </c>
@@ -3939,7 +4421,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.95" customHeight="1">
+    <row r="37" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>5</v>
       </c>
@@ -3957,7 +4439,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.95" customHeight="1">
+    <row r="38" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17">
         <v>6</v>
       </c>
@@ -3975,7 +4457,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17">
         <v>7</v>
       </c>
@@ -3993,7 +4475,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.95" customHeight="1">
+    <row r="40" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
@@ -4001,7 +4483,7 @@
       <c r="E40" s="31"/>
       <c r="F40" s="33"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" thickBot="1">
+    <row r="41" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21"/>
       <c r="B41" s="32"/>
       <c r="C41" s="32"/>
@@ -4014,7 +4496,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>LEFT(CELL("format",C9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4024,11 +4506,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A60181E-6CC8-4AB9-AAAE-CB7CFC66AE4A}">
   <sheetPr codeName="Feuil3"/>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -4039,13 +4521,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(C8:C16,"&lt;&gt;")</f>
+        <v>9</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -4057,13 +4564,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -4072,11 +4579,11 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -4096,7 +4603,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -4116,7 +4623,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -4136,7 +4643,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -4156,7 +4663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>4</v>
       </c>
@@ -4180,7 +4687,7 @@
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>5</v>
       </c>
@@ -4200,7 +4707,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>6</v>
       </c>
@@ -4220,7 +4727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>7</v>
       </c>
@@ -4240,7 +4747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21">
         <v>8</v>
       </c>
@@ -4260,7 +4767,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -4269,7 +4776,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="24" t="s">
         <v>40</v>
@@ -4279,7 +4786,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -4288,7 +4795,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>36</v>
       </c>
@@ -4308,7 +4815,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
       <c r="B21" s="12"/>
       <c r="C21" s="10"/>
@@ -4316,7 +4823,7 @@
       <c r="E21" s="10"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="15"/>
       <c r="C22" s="9"/>
@@ -4324,7 +4831,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="18"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -4332,7 +4839,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -4340,7 +4847,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4348,7 +4855,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4356,7 +4863,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4365,7 +4872,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="24" t="s">
         <v>155</v>
@@ -4375,7 +4882,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -4384,7 +4891,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -4401,49 +4908,49 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="12"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="20"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="18"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="18"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="18"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="18"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21"/>
       <c r="B39" s="23"/>
       <c r="C39" s="11"/>
@@ -4455,7 +4962,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>LEFT(CELL("format",C9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4465,11 +4972,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7C961E-DF0B-4DC1-8913-77C7CA803D3E}">
   <sheetPr codeName="Feuil4"/>
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -4480,13 +4987,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(C9:C16,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -4498,13 +5030,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -4513,11 +5045,11 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -4537,7 +5069,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -4547,7 +5079,7 @@
       <c r="E9" s="10"/>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -4557,7 +5089,7 @@
       <c r="E10" s="9"/>
       <c r="F10" s="18"/>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -4567,7 +5099,7 @@
       <c r="E11" s="9"/>
       <c r="F11" s="18"/>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>4</v>
       </c>
@@ -4578,7 +5110,7 @@
       <c r="F12" s="18"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>5</v>
       </c>
@@ -4588,7 +5120,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>6</v>
       </c>
@@ -4598,7 +5130,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>7</v>
       </c>
@@ -4608,7 +5140,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21">
         <v>8</v>
       </c>
@@ -4618,7 +5150,7 @@
       <c r="E16" s="11"/>
       <c r="F16" s="22"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -4627,7 +5159,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="24" t="s">
         <v>40</v>
@@ -4637,7 +5169,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -4646,7 +5178,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>36</v>
       </c>
@@ -4666,7 +5198,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>1</v>
       </c>
@@ -4686,7 +5218,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>2</v>
       </c>
@@ -4706,7 +5238,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -4714,7 +5246,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -4722,7 +5254,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4730,7 +5262,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4738,7 +5270,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -4747,7 +5279,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="24" t="s">
         <v>155</v>
@@ -4757,7 +5289,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -4766,7 +5298,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -4783,49 +5315,49 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="12"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="20"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="18"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="15"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="18"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="15"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="18"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="15"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="18"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21"/>
       <c r="B39" s="23"/>
       <c r="C39" s="11"/>
@@ -4837,7 +5369,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>LEFT(CELL("format",C9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4846,11 +5378,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97477491-CCFE-4825-8FB0-E6C9077B7A2A}">
   <sheetPr codeName="Feuil5"/>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -4861,13 +5393,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(C9:C16,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -4879,13 +5436,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -4894,11 +5451,11 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -4921,7 +5478,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -4944,7 +5501,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -4967,7 +5524,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -4990,7 +5547,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="9"/>
       <c r="C12" s="37"/>
@@ -4999,7 +5556,7 @@
       <c r="F12" s="18"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="9"/>
       <c r="C13" s="37"/>
@@ -5007,7 +5564,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="18"/>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="9"/>
       <c r="C14" s="37"/>
@@ -5015,7 +5572,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="18"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="9"/>
       <c r="C15" s="37"/>
@@ -5023,7 +5580,7 @@
       <c r="E15" s="9"/>
       <c r="F15" s="18"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21"/>
       <c r="B16" s="11"/>
       <c r="C16" s="23"/>
@@ -5031,7 +5588,7 @@
       <c r="E16" s="11"/>
       <c r="F16" s="22"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -5040,7 +5597,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="24" t="s">
         <v>40</v>
@@ -5050,7 +5607,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -5059,7 +5616,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>36</v>
       </c>
@@ -5079,7 +5636,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>1</v>
       </c>
@@ -5099,7 +5656,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="37"/>
       <c r="C22" s="9"/>
@@ -5107,7 +5664,7 @@
       <c r="E22" s="9"/>
       <c r="F22" s="18"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="37"/>
       <c r="C23" s="9"/>
@@ -5115,7 +5672,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="37"/>
       <c r="C24" s="9"/>
@@ -5123,7 +5680,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="37"/>
       <c r="C25" s="9"/>
@@ -5131,7 +5688,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="38"/>
       <c r="C26" s="11"/>
@@ -5139,7 +5696,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5148,7 +5705,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="24" t="s">
         <v>155</v>
@@ -5158,7 +5715,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -5167,7 +5724,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -5184,56 +5741,56 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="36"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="20"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="37"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="18"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="37"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="37"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="18"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="37"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="18"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="37"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="18"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21"/>
       <c r="B39" s="38"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="22"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D46" s="35"/>
     </row>
   </sheetData>
@@ -5241,7 +5798,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9:G11">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>LEFT(CELL("format",C9))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5256,11 +5813,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAF4AB9-9AAE-4FCC-9309-B2B545768411}">
   <sheetPr codeName="Feuil6"/>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -5271,13 +5828,38 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="H1" s="50">
+        <f>COUNTIF(C9:C16,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="F2" s="50">
+        <f>COUNTIFS(B20:B29,"&lt;&gt;",C20:C29,"VH")</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="50">
+        <f>COUNTA(C21:C29)-F2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="52">
+        <f>COUNTIF(E20:E29,"VIDE")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43" t="s">
         <v>53</v>
       </c>
@@ -5289,13 +5871,13 @@
       <c r="G3" s="43"/>
       <c r="H3" s="43"/>
     </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="24.95" customHeight="1">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="24" t="s">
         <v>39</v>
@@ -5304,11 +5886,11 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" thickBot="1">
+    <row r="7" spans="1:10" s="1" customFormat="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -5331,7 +5913,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>1</v>
       </c>
@@ -5354,7 +5936,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -5377,7 +5959,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>3</v>
       </c>
@@ -5400,7 +5982,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="9"/>
       <c r="C12" s="37"/>
@@ -5410,7 +5992,7 @@
       <c r="G12" s="5"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
       <c r="B13" s="9"/>
       <c r="C13" s="37"/>
@@ -5419,7 +6001,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17"/>
       <c r="B14" s="9"/>
       <c r="C14" s="37"/>
@@ -5428,7 +6010,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="9"/>
       <c r="C15" s="37"/>
@@ -5437,7 +6019,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21"/>
       <c r="B16" s="11"/>
       <c r="C16" s="23"/>
@@ -5446,7 +6028,7 @@
       <c r="F16" s="22"/>
       <c r="G16" s="5"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1"/>
@@ -5455,7 +6037,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="24" t="s">
         <v>40</v>
@@ -5465,7 +6047,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" ht="16.5" thickBot="1">
+    <row r="19" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>
@@ -5474,7 +6056,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" ht="16.5" thickBot="1">
+    <row r="20" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>36</v>
       </c>
@@ -5495,7 +6077,7 @@
       </c>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19"/>
       <c r="B21" s="36"/>
       <c r="C21" s="10"/>
@@ -5504,7 +6086,7 @@
       <c r="F21" s="20"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
       <c r="B22" s="37"/>
       <c r="C22" s="9"/>
@@ -5513,7 +6095,7 @@
       <c r="F22" s="18"/>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="37"/>
       <c r="C23" s="9"/>
@@ -5521,7 +6103,7 @@
       <c r="E23" s="9"/>
       <c r="F23" s="18"/>
     </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="17"/>
       <c r="B24" s="37"/>
       <c r="C24" s="9"/>
@@ -5529,7 +6111,7 @@
       <c r="E24" s="9"/>
       <c r="F24" s="18"/>
     </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17"/>
       <c r="B25" s="37"/>
       <c r="C25" s="9"/>
@@ -5537,7 +6119,7 @@
       <c r="E25" s="9"/>
       <c r="F25" s="18"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21"/>
       <c r="B26" s="38"/>
       <c r="C26" s="11"/>
@@ -5545,7 +6127,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5554,7 +6136,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="24" t="s">
         <v>155</v>
@@ -5564,7 +6146,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="1"/>
@@ -5573,7 +6155,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>36</v>
       </c>
@@ -5590,56 +6172,56 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
       <c r="B33" s="36"/>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="20"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="17"/>
       <c r="B34" s="37"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="18"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17"/>
       <c r="B35" s="37"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="17"/>
       <c r="B36" s="37"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="18"/>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17"/>
       <c r="B37" s="37"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="18"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="17"/>
       <c r="B38" s="37"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="18"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="21"/>
       <c r="B39" s="38"/>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
       <c r="E39" s="22"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D46" s="35"/>
     </row>
   </sheetData>
@@ -5647,7 +6229,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="G9:G11">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>LEFT(CELL("format",C9))</formula>
     </cfRule>
   </conditionalFormatting>
